--- a/artfynd/A 5747-2024 artfynd.xlsx
+++ b/artfynd/A 5747-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AY47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,61 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115036932</v>
+        <v>115510864</v>
       </c>
       <c r="B2" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mars-24-185, Ög</t>
+          <t>Mossarp, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572097</v>
+        <v>572025</v>
       </c>
       <c r="R2" t="n">
-        <v>6461817</v>
+        <v>6461810</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,12 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-16</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt förekommande, även fruktkroppar finns.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -767,33 +759,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jonas Lindebring</t>
+          <t>Karin Wilhelmsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jonas Lindebring</t>
+          <t>Karin Wilhelmsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115510846</v>
+        <v>115510865</v>
       </c>
       <c r="B3" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,21 +789,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -825,10 +813,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572136</v>
+        <v>572019</v>
       </c>
       <c r="R3" t="n">
-        <v>6461975</v>
+        <v>6461828</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,7 +853,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På gammal tall, här finns även silverfuror, i värdekärna klass 1.</t>
+          <t>Mycket rikligt både på lågor och stubbar av tall, samt på gammal rotvälta av en.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,6 +862,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -892,15 +881,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115510840</v>
+        <v>115510876</v>
       </c>
       <c r="B4" t="n">
-        <v>79099</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +892,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572006</v>
+        <v>572206</v>
       </c>
       <c r="R4" t="n">
-        <v>6461833</v>
+        <v>6461795</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,6 +952,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-03-16</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På tallåga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,15 +983,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115510842</v>
+        <v>115510878</v>
       </c>
       <c r="B5" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1010,21 +994,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1034,10 +1018,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572236</v>
+        <v>572364</v>
       </c>
       <c r="R5" t="n">
-        <v>6462028</v>
+        <v>6461924</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1070,6 +1054,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-03-16</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Med fruktkroppar</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1096,15 +1085,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115510839</v>
+        <v>115510882</v>
       </c>
       <c r="B6" t="n">
-        <v>79099</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1112,21 +1096,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1136,10 +1120,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>572079</v>
+        <v>572191</v>
       </c>
       <c r="R6" t="n">
-        <v>6461806</v>
+        <v>6461994</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1172,6 +1156,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-03-16</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gott om, även med fruktkroppar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1198,15 +1187,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115510838</v>
+        <v>115510883</v>
       </c>
       <c r="B7" t="n">
-        <v>79099</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1214,21 +1198,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1238,10 +1222,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>572249</v>
+        <v>572389</v>
       </c>
       <c r="R7" t="n">
-        <v>6461798</v>
+        <v>6462060</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1274,11 +1258,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-03-16</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På tallåga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1305,15 +1284,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>115510845</v>
+        <v>115510884</v>
       </c>
       <c r="B8" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1321,21 +1295,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1345,10 +1319,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>572289</v>
+        <v>572314</v>
       </c>
       <c r="R8" t="n">
-        <v>6461768</v>
+        <v>6461833</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1381,11 +1355,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-03-16</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Minst 2 st, häckningsrevir.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1412,15 +1381,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>115510884</v>
+        <v>115510885</v>
       </c>
       <c r="B9" t="n">
-        <v>78157</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1452,10 +1416,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>572314</v>
+        <v>572225</v>
       </c>
       <c r="R9" t="n">
-        <v>6461833</v>
+        <v>6461840</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1514,15 +1478,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>115510877</v>
+        <v>115510842</v>
       </c>
       <c r="B10" t="n">
-        <v>79099</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1530,21 +1489,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1554,10 +1513,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>572364</v>
+        <v>572236</v>
       </c>
       <c r="R10" t="n">
-        <v>6461924</v>
+        <v>6462028</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,15 +1575,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>115510853</v>
+        <v>115510870</v>
       </c>
       <c r="B11" t="n">
-        <v>56481</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1632,21 +1586,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102613</v>
+        <v>5420</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1656,10 +1610,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>572058</v>
+        <v>572263</v>
       </c>
       <c r="R11" t="n">
-        <v>6461803</v>
+        <v>6461837</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1692,11 +1646,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-03-16</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1723,15 +1672,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>115510892</v>
+        <v>115510846</v>
       </c>
       <c r="B12" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1739,21 +1683,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1763,10 +1707,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>572252</v>
+        <v>572136</v>
       </c>
       <c r="R12" t="n">
-        <v>6461824</v>
+        <v>6461975</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1803,7 +1747,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>På gammal tall, här finns även silverfuror, i värdekärna klass 1.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1830,37 +1774,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>115510826</v>
+        <v>115510848</v>
       </c>
       <c r="B13" t="n">
-        <v>5185</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>105930</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1870,10 +1809,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>572222</v>
+        <v>572212</v>
       </c>
       <c r="R13" t="n">
-        <v>6462030</v>
+        <v>6461985</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,37 +1871,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>115510843</v>
+        <v>115510850</v>
       </c>
       <c r="B14" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1972,10 +1906,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>572202</v>
+        <v>572348</v>
       </c>
       <c r="R14" t="n">
-        <v>6462095</v>
+        <v>6461978</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2008,11 +1942,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-03-16</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2039,15 +1968,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>115510882</v>
+        <v>115510852</v>
       </c>
       <c r="B15" t="n">
-        <v>78157</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2055,21 +1979,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2079,10 +2003,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>572191</v>
+        <v>572372</v>
       </c>
       <c r="R15" t="n">
-        <v>6461994</v>
+        <v>6461925</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2115,11 +2039,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-03-16</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Gott om, även med fruktkroppar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2146,37 +2065,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>115510864</v>
+        <v>115510829</v>
       </c>
       <c r="B16" t="n">
-        <v>78157</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2186,10 +2100,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>572025</v>
+        <v>572309</v>
       </c>
       <c r="R16" t="n">
-        <v>6461810</v>
+        <v>6462013</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2226,7 +2140,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Rikligt förekommande, även fruktkroppar finns.</t>
+          <t>På grov granlåga.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2235,7 +2149,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2254,58 +2167,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>115510869</v>
+        <v>115510830</v>
       </c>
       <c r="B17" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Mossarp, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>572350</v>
+        <v>572200</v>
       </c>
       <c r="R17" t="n">
-        <v>6462038</v>
+        <v>6462088</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2340,18 +2240,12 @@
           <t>2024-03-16</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>20 st</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2370,15 +2264,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>115510830</v>
+        <v>115510831</v>
       </c>
       <c r="B18" t="n">
-        <v>79099</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2410,10 +2299,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>572200</v>
+        <v>572400</v>
       </c>
       <c r="R18" t="n">
-        <v>6462088</v>
+        <v>6462034</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2472,37 +2361,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>115510870</v>
+        <v>115510832</v>
       </c>
       <c r="B19" t="n">
-        <v>90735</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5420</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2512,10 +2396,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>572263</v>
+        <v>572367</v>
       </c>
       <c r="R19" t="n">
-        <v>6461837</v>
+        <v>6462015</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2548,6 +2432,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-03-16</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Tallstubben är huggen med yxa och visar på trädkontinuitet tillbaka till 1650-talet, då trädet högs för minst 150 år sedan och var då 300 år.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2574,37 +2463,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>115510829</v>
+        <v>115510833</v>
       </c>
       <c r="B20" t="n">
-        <v>90297</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2614,10 +2498,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>572309</v>
+        <v>572347</v>
       </c>
       <c r="R20" t="n">
-        <v>6462013</v>
+        <v>6461955</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2650,11 +2534,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-03-16</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På grov granlåga.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2681,58 +2560,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>115510868</v>
+        <v>115510835</v>
       </c>
       <c r="B21" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Mossarp, Ög</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>572356</v>
+        <v>572390</v>
       </c>
       <c r="R21" t="n">
-        <v>6462048</v>
+        <v>6461915</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2769,7 +2635,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>12 st</t>
+          <t>Tallåga helt övervuxen av vedskivlav.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2778,7 +2644,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2797,15 +2662,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>115510863</v>
+        <v>115510836</v>
       </c>
       <c r="B22" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2813,21 +2673,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2837,10 +2697,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>572019</v>
+        <v>572338</v>
       </c>
       <c r="R22" t="n">
-        <v>6461806</v>
+        <v>6461858</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2873,11 +2733,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-03-16</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Födosök</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2904,15 +2759,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>115510878</v>
+        <v>115510837</v>
       </c>
       <c r="B23" t="n">
-        <v>78157</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2920,21 +2770,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2944,10 +2794,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>572364</v>
+        <v>572323</v>
       </c>
       <c r="R23" t="n">
-        <v>6461924</v>
+        <v>6461822</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2980,11 +2830,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-03-16</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Med fruktkroppar</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3011,37 +2856,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>115510867</v>
+        <v>115510838</v>
       </c>
       <c r="B24" t="n">
-        <v>56481</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102613</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3051,10 +2891,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>572343</v>
+        <v>572249</v>
       </c>
       <c r="R24" t="n">
-        <v>6461975</v>
+        <v>6461798</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3091,7 +2931,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>En hög med spillning efter orrens "värme-element" på vintern.</t>
+          <t>På tallåga</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3118,15 +2958,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>115510832</v>
+        <v>115510839</v>
       </c>
       <c r="B25" t="n">
-        <v>79099</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3158,10 +2993,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>572367</v>
+        <v>572079</v>
       </c>
       <c r="R25" t="n">
-        <v>6462015</v>
+        <v>6461806</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3194,11 +3029,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-03-16</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Tallstubben är huggen med yxa och visar på trädkontinuitet tillbaka till 1650-talet, då trädet högs för minst 150 år sedan och var då 300 år.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3225,15 +3055,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>115510875</v>
+        <v>115510840</v>
       </c>
       <c r="B26" t="n">
-        <v>79099</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3265,10 +3090,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>572206</v>
+        <v>572006</v>
       </c>
       <c r="R26" t="n">
-        <v>6461795</v>
+        <v>6461833</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3301,11 +3126,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-03-16</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På tallåga</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3332,15 +3152,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>115510833</v>
+        <v>115510875</v>
       </c>
       <c r="B27" t="n">
-        <v>79099</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3372,10 +3187,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>572347</v>
+        <v>572206</v>
       </c>
       <c r="R27" t="n">
-        <v>6461955</v>
+        <v>6461795</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3408,6 +3223,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-03-16</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På tallåga</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3434,15 +3254,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>115510865</v>
+        <v>115510877</v>
       </c>
       <c r="B28" t="n">
-        <v>78157</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3450,21 +3265,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3474,10 +3289,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>572019</v>
+        <v>572364</v>
       </c>
       <c r="R28" t="n">
-        <v>6461828</v>
+        <v>6461924</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3512,18 +3327,12 @@
           <t>2024-03-16</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Mycket rikligt både på lågor och stubbar av tall, samt på gammal rotvälta av en.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3542,15 +3351,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>115510883</v>
+        <v>115510881</v>
       </c>
       <c r="B29" t="n">
-        <v>78157</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3558,21 +3362,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3582,10 +3386,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>572389</v>
+        <v>572191</v>
       </c>
       <c r="R29" t="n">
-        <v>6462060</v>
+        <v>6461994</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3644,15 +3448,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>115510828</v>
+        <v>115510862</v>
       </c>
       <c r="B30" t="n">
-        <v>5165</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3660,21 +3459,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3684,10 +3483,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>572309</v>
+        <v>571996</v>
       </c>
       <c r="R30" t="n">
-        <v>6462013</v>
+        <v>6461835</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3724,7 +3523,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På grov granlåga.</t>
+          <t>Födosök, både äldre och nyare.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3751,37 +3550,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>115510885</v>
+        <v>115510863</v>
       </c>
       <c r="B31" t="n">
-        <v>78157</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3791,10 +3585,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>572225</v>
+        <v>572019</v>
       </c>
       <c r="R31" t="n">
-        <v>6461840</v>
+        <v>6461806</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3827,6 +3621,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-03-16</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3853,37 +3652,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>115510879</v>
+        <v>115510892</v>
       </c>
       <c r="B32" t="n">
-        <v>5466</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>101920</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3893,10 +3687,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>572191</v>
+        <v>572252</v>
       </c>
       <c r="R32" t="n">
-        <v>6461994</v>
+        <v>6461824</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3929,6 +3723,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-03-16</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3955,53 +3754,56 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>115510881</v>
+        <v>115036932</v>
       </c>
       <c r="B33" t="n">
-        <v>79099</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Mossarp, Ög</t>
+          <t>Mars-24-185, Ög</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>572191</v>
+        <v>572097</v>
       </c>
       <c r="R33" t="n">
-        <v>6461994</v>
+        <v>6461817</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4025,12 +3827,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4045,27 +3847,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Karin Wilhelmsson</t>
+          <t>Jonas Lindebring</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Karin Wilhelmsson</t>
+          <t>Jonas Lindebring</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>115510873</v>
+        <v>115510843</v>
       </c>
       <c r="B34" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4097,10 +3894,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>572105</v>
+        <v>572202</v>
       </c>
       <c r="R34" t="n">
-        <v>6461832</v>
+        <v>6462095</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4137,7 +3934,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Spillning, indikationer på spelplats.</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4164,37 +3961,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>115510876</v>
+        <v>115510844</v>
       </c>
       <c r="B35" t="n">
-        <v>78157</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4204,10 +3996,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>572206</v>
+        <v>572348</v>
       </c>
       <c r="R35" t="n">
-        <v>6461795</v>
+        <v>6461976</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4244,7 +4036,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På tallåga</t>
+          <t>Färsk spillning</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4271,15 +4063,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>115510844</v>
+        <v>115510873</v>
       </c>
       <c r="B36" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4311,10 +4098,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>572348</v>
+        <v>572105</v>
       </c>
       <c r="R36" t="n">
-        <v>6461976</v>
+        <v>6461832</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4351,7 +4138,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Färsk spillning</t>
+          <t>Spillning, indikationer på spelplats.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4378,37 +4165,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>115510852</v>
+        <v>115510828</v>
       </c>
       <c r="B37" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5442</v>
+        <v>100526</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4418,10 +4200,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>572372</v>
+        <v>572309</v>
       </c>
       <c r="R37" t="n">
-        <v>6461925</v>
+        <v>6462013</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4454,6 +4236,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-03-16</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På grov granlåga.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4480,53 +4267,69 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>115510837</v>
+        <v>81149623</v>
       </c>
       <c r="B38" t="n">
-        <v>79099</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5482</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>101920</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Linnaeus, 1767)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>fönsterfälla</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Mossarp, Ög</t>
+          <t>Östantorp, O Ögat, Ög</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>572323</v>
+        <v>572172</v>
       </c>
       <c r="R38" t="n">
-        <v>6461822</v>
+        <v>6461977</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4550,12 +4353,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>1997-07-13</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>1997-08-03</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4564,55 +4367,61 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>talllågor</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Karin Wilhelmsson</t>
+          <t>Göran Börkén</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Karin Wilhelmsson</t>
+          <t>Göran Börkén</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>115510831</v>
+        <v>115510879</v>
       </c>
       <c r="B39" t="n">
-        <v>79099</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5482</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>101920</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4622,10 +4431,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>572400</v>
+        <v>572191</v>
       </c>
       <c r="R39" t="n">
-        <v>6462034</v>
+        <v>6461994</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4684,58 +4493,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>115534242</v>
+        <v>115510853</v>
       </c>
       <c r="B40" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57144</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>102613</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Sluttning 2, Yxnerums kyrka, Ög</t>
+          <t>Mossarp, Ög</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>572248</v>
+        <v>572058</v>
       </c>
       <c r="R40" t="n">
-        <v>6462117</v>
+        <v>6461803</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4762,12 +4558,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-16</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4776,77 +4577,63 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Carina Faxén</t>
+          <t>Karin Wilhelmsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Carina Faxén</t>
+          <t>Karin Wilhelmsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>115533865</v>
+        <v>115510867</v>
       </c>
       <c r="B41" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57144</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>102613</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>sänkan 1, Yxnerums kyrka, Ög</t>
+          <t>Mossarp, Ög</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>572294</v>
+        <v>572343</v>
       </c>
       <c r="R41" t="n">
-        <v>6462088</v>
+        <v>6461975</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4873,22 +4660,17 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2024-03-16</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>En hög med spillning efter orrens "värme-element" på vintern.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4897,34 +4679,28 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Carina Faxén</t>
+          <t>Karin Wilhelmsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Carina Faxén</t>
+          <t>Karin Wilhelmsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>115510850</v>
+        <v>115510845</v>
       </c>
       <c r="B42" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4932,21 +4708,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4956,10 +4732,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>572348</v>
+        <v>572289</v>
       </c>
       <c r="R42" t="n">
-        <v>6461978</v>
+        <v>6461768</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4994,6 +4770,11 @@
           <t>2024-03-16</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Minst 2 st, häckningsrevir.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5015,6 +4796,547 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>115510826</v>
+      </c>
+      <c r="B43" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Mossarp, Ög</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>572222</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6462030</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Yxnerum</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-03-16</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-03-16</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Karin Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Karin Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>115510868</v>
+      </c>
+      <c r="B44" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Mossarp, Ög</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>572356</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6462048</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Yxnerum</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-03-16</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-03-16</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>12 st</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Karin Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Karin Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>115510869</v>
+      </c>
+      <c r="B45" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Mossarp, Ög</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>572350</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6462038</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Yxnerum</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-03-16</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-03-16</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>20 st</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Karin Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Karin Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>115533865</v>
+      </c>
+      <c r="B46" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>sänkan 1, Yxnerums kyrka, Ög</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>572294</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6462088</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Yxnerum</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-03-23</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-03-23</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Carina Faxén</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Carina Faxén</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>115534242</v>
+      </c>
+      <c r="B47" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Sluttning 2, Yxnerums kyrka, Ög</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>572248</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6462117</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Yxnerum</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-03-23</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-03-23</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Carina Faxén</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Carina Faxén</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5747-2024 artfynd.xlsx
+++ b/artfynd/A 5747-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY47"/>
+  <dimension ref="A1:AZ47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -775,6 +780,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115510864</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -878,6 +888,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115510865</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115510876</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1082,6 +1102,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115510878</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1184,6 +1209,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115510882</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1281,6 +1311,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115510883</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1378,6 +1413,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115510884</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1475,6 +1515,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115510885</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1572,6 +1617,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115510842</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1669,6 +1719,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115510870</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1771,6 +1826,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115510846</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1868,6 +1928,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115510848</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1965,6 +2030,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115510850</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2062,6 +2132,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115510852</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2164,6 +2239,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115510829</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2261,6 +2341,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115510830</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2358,6 +2443,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115510831</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2460,6 +2550,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115510832</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2557,6 +2652,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115510833</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2659,6 +2759,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115510835</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2756,6 +2861,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115510836</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2853,6 +2963,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115510837</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2955,6 +3070,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115510838</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3052,6 +3172,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115510839</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3149,6 +3274,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115510840</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3251,6 +3381,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115510875</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3348,6 +3483,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115510877</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3445,6 +3585,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115510881</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3547,6 +3692,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115510862</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3649,6 +3799,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115510863</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3751,6 +3906,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115510892</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3856,6 +4016,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115036932</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3958,6 +4123,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115510843</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4060,6 +4230,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115510844</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4162,6 +4337,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115510873</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4264,6 +4444,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115510828</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4393,6 +4578,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81149623</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4490,6 +4680,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115510879</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4592,6 +4787,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115510853</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4694,6 +4894,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115510867</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4796,6 +5001,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115510845</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4893,6 +5103,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115510826</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5004,6 +5219,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115510868</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5115,6 +5335,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115510869</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5231,6 +5456,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115533865</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5337,8 +5567,61 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115534242</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>